--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProdTerminationRegist001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProdTerminationRegist001.xlsx
@@ -815,27 +815,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R298"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="16.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="5" customWidth="1"/>
     <col min="3" max="3" width="23" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.75" style="17" customWidth="1"/>
-    <col min="5" max="5" width="18.625" style="17" customWidth="1"/>
+    <col min="4" max="4" width="24.7265625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="18.6328125" style="17" customWidth="1"/>
     <col min="6" max="6" width="23" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21" style="12" customWidth="1"/>
-    <col min="8" max="9" width="20.75" style="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.25" style="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.5" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="20.7265625" style="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.26953125" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.453125" style="17" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="23" style="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.75" style="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.625" style="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.7265625" style="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29.6328125" style="17" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="23" style="19" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>27</v>
       </c>
@@ -891,7 +891,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="13"/>
@@ -913,7 +913,7 @@
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="13"/>
@@ -935,7 +935,7 @@
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="13"/>
@@ -957,7 +957,7 @@
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="13"/>
@@ -979,7 +979,7 @@
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="13"/>
@@ -1001,7 +1001,7 @@
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="13"/>
@@ -1021,7 +1021,7 @@
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="13"/>
@@ -1043,7 +1043,7 @@
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="13"/>
@@ -1065,7 +1065,7 @@
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="13"/>
@@ -1087,7 +1087,7 @@
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="13"/>
@@ -1109,7 +1109,7 @@
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="13"/>
@@ -1131,7 +1131,7 @@
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="13"/>
@@ -1153,7 +1153,7 @@
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="13"/>
@@ -1175,7 +1175,7 @@
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="13"/>
@@ -1197,7 +1197,7 @@
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="13"/>
@@ -1219,7 +1219,7 @@
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="13"/>
@@ -1241,7 +1241,7 @@
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="13"/>
@@ -1263,7 +1263,7 @@
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="13"/>
@@ -1285,7 +1285,7 @@
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="13"/>
@@ -1307,7 +1307,7 @@
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
       <c r="C21" s="13"/>
@@ -1329,7 +1329,7 @@
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="13"/>
@@ -1351,7 +1351,7 @@
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="13"/>
@@ -1373,7 +1373,7 @@
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="13"/>
@@ -1395,7 +1395,7 @@
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="13"/>
@@ -1417,7 +1417,7 @@
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="13"/>
@@ -1439,7 +1439,7 @@
       <c r="Q26" s="8"/>
       <c r="R26" s="8"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="13"/>
@@ -1461,7 +1461,7 @@
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="13"/>
@@ -1483,7 +1483,7 @@
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="13"/>
@@ -1505,7 +1505,7 @@
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="13"/>
@@ -1527,7 +1527,7 @@
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="13"/>
@@ -1549,7 +1549,7 @@
       <c r="Q31" s="8"/>
       <c r="R31" s="8"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="13"/>
@@ -1571,7 +1571,7 @@
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="13"/>
@@ -1593,7 +1593,7 @@
       <c r="Q33" s="8"/>
       <c r="R33" s="8"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="13"/>
@@ -1615,7 +1615,7 @@
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="13"/>
@@ -1637,7 +1637,7 @@
       <c r="Q35" s="8"/>
       <c r="R35" s="8"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="13"/>
@@ -1659,7 +1659,7 @@
       <c r="Q36" s="8"/>
       <c r="R36" s="8"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="13"/>
@@ -1681,7 +1681,7 @@
       <c r="Q37" s="8"/>
       <c r="R37" s="8"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="13"/>
@@ -1703,7 +1703,7 @@
       <c r="Q38" s="8"/>
       <c r="R38" s="8"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="13"/>
@@ -1725,7 +1725,7 @@
       <c r="Q39" s="8"/>
       <c r="R39" s="8"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="13"/>
@@ -1747,7 +1747,7 @@
       <c r="Q40" s="8"/>
       <c r="R40" s="8"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="13"/>
@@ -1769,7 +1769,7 @@
       <c r="Q41" s="8"/>
       <c r="R41" s="8"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="13"/>
@@ -1791,7 +1791,7 @@
       <c r="Q42" s="8"/>
       <c r="R42" s="8"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="13"/>
@@ -1813,7 +1813,7 @@
       <c r="Q43" s="8"/>
       <c r="R43" s="8"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="13"/>
@@ -1835,7 +1835,7 @@
       <c r="Q44" s="8"/>
       <c r="R44" s="8"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="13"/>
@@ -1857,7 +1857,7 @@
       <c r="Q45" s="8"/>
       <c r="R45" s="8"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="13"/>
@@ -1879,7 +1879,7 @@
       <c r="Q46" s="8"/>
       <c r="R46" s="8"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="13"/>
@@ -1901,7 +1901,7 @@
       <c r="Q47" s="8"/>
       <c r="R47" s="8"/>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="13"/>
@@ -1923,7 +1923,7 @@
       <c r="Q48" s="8"/>
       <c r="R48" s="8"/>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="13"/>
@@ -1945,7 +1945,7 @@
       <c r="Q49" s="8"/>
       <c r="R49" s="8"/>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="13"/>
@@ -1967,7 +1967,7 @@
       <c r="Q50" s="8"/>
       <c r="R50" s="8"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="13"/>
@@ -1989,7 +1989,7 @@
       <c r="Q51" s="8"/>
       <c r="R51" s="8"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="13"/>
@@ -2011,7 +2011,7 @@
       <c r="Q52" s="8"/>
       <c r="R52" s="8"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
       <c r="C53" s="13"/>
@@ -2033,7 +2033,7 @@
       <c r="Q53" s="8"/>
       <c r="R53" s="8"/>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="13"/>
@@ -2055,7 +2055,7 @@
       <c r="Q54" s="8"/>
       <c r="R54" s="8"/>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="13"/>
@@ -2077,7 +2077,7 @@
       <c r="Q55" s="8"/>
       <c r="R55" s="8"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="13"/>
@@ -2099,7 +2099,7 @@
       <c r="Q56" s="8"/>
       <c r="R56" s="8"/>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
       <c r="C57" s="13"/>
@@ -2121,7 +2121,7 @@
       <c r="Q57" s="8"/>
       <c r="R57" s="8"/>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="9"/>
       <c r="B58" s="9"/>
       <c r="C58" s="13"/>
@@ -2143,7 +2143,7 @@
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="9"/>
       <c r="B59" s="9"/>
       <c r="C59" s="13"/>
@@ -2165,7 +2165,7 @@
       <c r="Q59" s="8"/>
       <c r="R59" s="8"/>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="9"/>
       <c r="B60" s="9"/>
       <c r="C60" s="13"/>
@@ -2187,7 +2187,7 @@
       <c r="Q60" s="8"/>
       <c r="R60" s="8"/>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="9"/>
       <c r="B61" s="9"/>
       <c r="C61" s="13"/>
@@ -2209,7 +2209,7 @@
       <c r="Q61" s="8"/>
       <c r="R61" s="8"/>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="9"/>
       <c r="B62" s="9"/>
       <c r="C62" s="13"/>
@@ -2231,7 +2231,7 @@
       <c r="Q62" s="8"/>
       <c r="R62" s="8"/>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="9"/>
       <c r="B63" s="9"/>
       <c r="C63" s="13"/>
@@ -2253,7 +2253,7 @@
       <c r="Q63" s="8"/>
       <c r="R63" s="8"/>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="9"/>
       <c r="B64" s="9"/>
       <c r="C64" s="13"/>
@@ -2275,7 +2275,7 @@
       <c r="Q64" s="8"/>
       <c r="R64" s="8"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="9"/>
       <c r="B65" s="9"/>
       <c r="C65" s="13"/>
@@ -2297,7 +2297,7 @@
       <c r="Q65" s="8"/>
       <c r="R65" s="8"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="9"/>
       <c r="B66" s="9"/>
       <c r="C66" s="13"/>
@@ -2319,7 +2319,7 @@
       <c r="Q66" s="8"/>
       <c r="R66" s="8"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="9"/>
       <c r="B67" s="9"/>
       <c r="C67" s="13"/>
@@ -2341,7 +2341,7 @@
       <c r="Q67" s="8"/>
       <c r="R67" s="8"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="9"/>
       <c r="B68" s="9"/>
       <c r="C68" s="13"/>
@@ -2363,7 +2363,7 @@
       <c r="Q68" s="8"/>
       <c r="R68" s="8"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="9"/>
       <c r="B69" s="9"/>
       <c r="C69" s="13"/>
@@ -2385,7 +2385,7 @@
       <c r="Q69" s="8"/>
       <c r="R69" s="8"/>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="9"/>
       <c r="B70" s="9"/>
       <c r="C70" s="13"/>
@@ -2407,7 +2407,7 @@
       <c r="Q70" s="8"/>
       <c r="R70" s="8"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
       <c r="C71" s="13"/>
@@ -2429,7 +2429,7 @@
       <c r="Q71" s="8"/>
       <c r="R71" s="8"/>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
       <c r="C72" s="13"/>
@@ -2451,7 +2451,7 @@
       <c r="Q72" s="8"/>
       <c r="R72" s="8"/>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
       <c r="C73" s="13"/>
@@ -2473,7 +2473,7 @@
       <c r="Q73" s="8"/>
       <c r="R73" s="8"/>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
       <c r="C74" s="13"/>
@@ -2495,7 +2495,7 @@
       <c r="Q74" s="8"/>
       <c r="R74" s="8"/>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
       <c r="C75" s="13"/>
@@ -2517,7 +2517,7 @@
       <c r="Q75" s="8"/>
       <c r="R75" s="8"/>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="9"/>
       <c r="B76" s="9"/>
       <c r="C76" s="13"/>
@@ -2539,7 +2539,7 @@
       <c r="Q76" s="8"/>
       <c r="R76" s="8"/>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="9"/>
       <c r="B77" s="9"/>
       <c r="C77" s="13"/>
@@ -2561,7 +2561,7 @@
       <c r="Q77" s="8"/>
       <c r="R77" s="8"/>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="9"/>
       <c r="B78" s="9"/>
       <c r="C78" s="13"/>
@@ -2583,7 +2583,7 @@
       <c r="Q78" s="8"/>
       <c r="R78" s="8"/>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="9"/>
       <c r="B79" s="9"/>
       <c r="C79" s="13"/>
@@ -2605,7 +2605,7 @@
       <c r="Q79" s="8"/>
       <c r="R79" s="8"/>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="9"/>
       <c r="B80" s="9"/>
       <c r="C80" s="13"/>
@@ -2627,7 +2627,7 @@
       <c r="Q80" s="8"/>
       <c r="R80" s="8"/>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="9"/>
       <c r="B81" s="9"/>
       <c r="C81" s="13"/>
@@ -2649,7 +2649,7 @@
       <c r="Q81" s="8"/>
       <c r="R81" s="8"/>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="9"/>
       <c r="B82" s="9"/>
       <c r="C82" s="13"/>
@@ -2671,7 +2671,7 @@
       <c r="Q82" s="8"/>
       <c r="R82" s="8"/>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="9"/>
       <c r="B83" s="9"/>
       <c r="C83" s="13"/>
@@ -2693,7 +2693,7 @@
       <c r="Q83" s="8"/>
       <c r="R83" s="8"/>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="9"/>
       <c r="B84" s="9"/>
       <c r="C84" s="13"/>
@@ -2715,7 +2715,7 @@
       <c r="Q84" s="8"/>
       <c r="R84" s="8"/>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="9"/>
       <c r="B85" s="9"/>
       <c r="C85" s="13"/>
@@ -2737,7 +2737,7 @@
       <c r="Q85" s="8"/>
       <c r="R85" s="8"/>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="9"/>
       <c r="B86" s="9"/>
       <c r="C86" s="13"/>
@@ -2759,7 +2759,7 @@
       <c r="Q86" s="8"/>
       <c r="R86" s="8"/>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="9"/>
       <c r="B87" s="9"/>
       <c r="C87" s="13"/>
@@ -2781,7 +2781,7 @@
       <c r="Q87" s="8"/>
       <c r="R87" s="8"/>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="9"/>
       <c r="B88" s="9"/>
       <c r="C88" s="13"/>
@@ -2803,7 +2803,7 @@
       <c r="Q88" s="8"/>
       <c r="R88" s="8"/>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="9"/>
       <c r="B89" s="9"/>
       <c r="C89" s="13"/>
@@ -2825,7 +2825,7 @@
       <c r="Q89" s="8"/>
       <c r="R89" s="8"/>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="9"/>
       <c r="B90" s="9"/>
       <c r="C90" s="13"/>
@@ -2847,7 +2847,7 @@
       <c r="Q90" s="8"/>
       <c r="R90" s="8"/>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="9"/>
       <c r="B91" s="9"/>
       <c r="C91" s="13"/>
@@ -2869,7 +2869,7 @@
       <c r="Q91" s="8"/>
       <c r="R91" s="8"/>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="9"/>
       <c r="B92" s="9"/>
       <c r="C92" s="13"/>
@@ -2891,7 +2891,7 @@
       <c r="Q92" s="8"/>
       <c r="R92" s="8"/>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="9"/>
       <c r="B93" s="9"/>
       <c r="C93" s="13"/>
@@ -2913,7 +2913,7 @@
       <c r="Q93" s="8"/>
       <c r="R93" s="8"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="9"/>
       <c r="B94" s="9"/>
       <c r="C94" s="13"/>
@@ -2935,7 +2935,7 @@
       <c r="Q94" s="8"/>
       <c r="R94" s="8"/>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="9"/>
       <c r="B95" s="9"/>
       <c r="C95" s="13"/>
@@ -2957,7 +2957,7 @@
       <c r="Q95" s="8"/>
       <c r="R95" s="8"/>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="9"/>
       <c r="B96" s="9"/>
       <c r="C96" s="13"/>
@@ -2979,7 +2979,7 @@
       <c r="Q96" s="8"/>
       <c r="R96" s="8"/>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="9"/>
       <c r="B97" s="9"/>
       <c r="C97" s="13"/>
@@ -3001,7 +3001,7 @@
       <c r="Q97" s="8"/>
       <c r="R97" s="8"/>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="9"/>
       <c r="B98" s="9"/>
       <c r="C98" s="13"/>
@@ -3023,7 +3023,7 @@
       <c r="Q98" s="8"/>
       <c r="R98" s="8"/>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="9"/>
       <c r="B99" s="9"/>
       <c r="C99" s="13"/>
@@ -3045,7 +3045,7 @@
       <c r="Q99" s="8"/>
       <c r="R99" s="8"/>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="9"/>
       <c r="B100" s="9"/>
       <c r="C100" s="13"/>
@@ -3067,7 +3067,7 @@
       <c r="Q100" s="8"/>
       <c r="R100" s="8"/>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="9"/>
       <c r="B101" s="9"/>
       <c r="C101" s="13"/>
@@ -3089,7 +3089,7 @@
       <c r="Q101" s="8"/>
       <c r="R101" s="8"/>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="9"/>
       <c r="B102" s="9"/>
       <c r="C102" s="13"/>
@@ -3111,7 +3111,7 @@
       <c r="Q102" s="8"/>
       <c r="R102" s="8"/>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="9"/>
       <c r="B103" s="9"/>
       <c r="C103" s="13"/>
@@ -3133,7 +3133,7 @@
       <c r="Q103" s="8"/>
       <c r="R103" s="8"/>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="9"/>
       <c r="B104" s="9"/>
       <c r="C104" s="13"/>
@@ -3155,7 +3155,7 @@
       <c r="Q104" s="8"/>
       <c r="R104" s="8"/>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="9"/>
       <c r="B105" s="9"/>
       <c r="C105" s="13"/>
@@ -3177,7 +3177,7 @@
       <c r="Q105" s="8"/>
       <c r="R105" s="8"/>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="9"/>
       <c r="B106" s="9"/>
       <c r="C106" s="13"/>
@@ -3199,7 +3199,7 @@
       <c r="Q106" s="8"/>
       <c r="R106" s="8"/>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="9"/>
       <c r="B107" s="9"/>
       <c r="C107" s="13"/>
@@ -3221,7 +3221,7 @@
       <c r="Q107" s="8"/>
       <c r="R107" s="8"/>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="9"/>
       <c r="B108" s="9"/>
       <c r="C108" s="13"/>
@@ -3243,7 +3243,7 @@
       <c r="Q108" s="8"/>
       <c r="R108" s="8"/>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="9"/>
       <c r="B109" s="9"/>
       <c r="C109" s="13"/>
@@ -3265,7 +3265,7 @@
       <c r="Q109" s="8"/>
       <c r="R109" s="8"/>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="9"/>
       <c r="B110" s="9"/>
       <c r="C110" s="13"/>
@@ -3287,7 +3287,7 @@
       <c r="Q110" s="8"/>
       <c r="R110" s="8"/>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="9"/>
       <c r="B111" s="9"/>
       <c r="C111" s="13"/>
@@ -3309,7 +3309,7 @@
       <c r="Q111" s="8"/>
       <c r="R111" s="8"/>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="9"/>
       <c r="B112" s="9"/>
       <c r="C112" s="13"/>
@@ -3331,7 +3331,7 @@
       <c r="Q112" s="8"/>
       <c r="R112" s="8"/>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="9"/>
       <c r="B113" s="9"/>
       <c r="C113" s="13"/>
@@ -3353,7 +3353,7 @@
       <c r="Q113" s="8"/>
       <c r="R113" s="8"/>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="9"/>
       <c r="B114" s="9"/>
       <c r="C114" s="13"/>
@@ -3375,7 +3375,7 @@
       <c r="Q114" s="8"/>
       <c r="R114" s="8"/>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="9"/>
       <c r="B115" s="9"/>
       <c r="C115" s="13"/>
@@ -3397,7 +3397,7 @@
       <c r="Q115" s="8"/>
       <c r="R115" s="8"/>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="9"/>
       <c r="B116" s="9"/>
       <c r="C116" s="13"/>
@@ -3419,7 +3419,7 @@
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="9"/>
       <c r="B117" s="9"/>
       <c r="C117" s="13"/>
@@ -3441,7 +3441,7 @@
       <c r="Q117" s="8"/>
       <c r="R117" s="8"/>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="9"/>
       <c r="B118" s="9"/>
       <c r="C118" s="13"/>
@@ -3463,7 +3463,7 @@
       <c r="Q118" s="8"/>
       <c r="R118" s="8"/>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="9"/>
       <c r="B119" s="9"/>
       <c r="C119" s="13"/>
@@ -3485,7 +3485,7 @@
       <c r="Q119" s="8"/>
       <c r="R119" s="8"/>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="9"/>
       <c r="B120" s="9"/>
       <c r="C120" s="13"/>
@@ -3507,7 +3507,7 @@
       <c r="Q120" s="8"/>
       <c r="R120" s="8"/>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="9"/>
       <c r="B121" s="9"/>
       <c r="C121" s="13"/>
@@ -3529,7 +3529,7 @@
       <c r="Q121" s="8"/>
       <c r="R121" s="8"/>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="9"/>
       <c r="B122" s="9"/>
       <c r="C122" s="13"/>
@@ -3551,7 +3551,7 @@
       <c r="Q122" s="8"/>
       <c r="R122" s="8"/>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="9"/>
       <c r="B123" s="9"/>
       <c r="C123" s="13"/>
@@ -3573,7 +3573,7 @@
       <c r="Q123" s="8"/>
       <c r="R123" s="8"/>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="9"/>
       <c r="B124" s="9"/>
       <c r="C124" s="13"/>
@@ -3595,7 +3595,7 @@
       <c r="Q124" s="8"/>
       <c r="R124" s="8"/>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="9"/>
       <c r="B125" s="9"/>
       <c r="C125" s="13"/>
@@ -3617,7 +3617,7 @@
       <c r="Q125" s="8"/>
       <c r="R125" s="8"/>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="9"/>
       <c r="B126" s="9"/>
       <c r="C126" s="13"/>
@@ -3639,7 +3639,7 @@
       <c r="Q126" s="8"/>
       <c r="R126" s="8"/>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="9"/>
       <c r="B127" s="9"/>
       <c r="C127" s="13"/>
@@ -3661,7 +3661,7 @@
       <c r="Q127" s="8"/>
       <c r="R127" s="8"/>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="9"/>
       <c r="B128" s="9"/>
       <c r="C128" s="13"/>
@@ -3683,7 +3683,7 @@
       <c r="Q128" s="8"/>
       <c r="R128" s="8"/>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="9"/>
       <c r="B129" s="9"/>
       <c r="C129" s="13"/>
@@ -3705,7 +3705,7 @@
       <c r="Q129" s="8"/>
       <c r="R129" s="8"/>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="9"/>
       <c r="B130" s="9"/>
       <c r="C130" s="13"/>
@@ -3727,7 +3727,7 @@
       <c r="Q130" s="8"/>
       <c r="R130" s="8"/>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" s="9"/>
       <c r="B131" s="9"/>
       <c r="C131" s="13"/>
@@ -3749,7 +3749,7 @@
       <c r="Q131" s="8"/>
       <c r="R131" s="8"/>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" s="9"/>
       <c r="B132" s="9"/>
       <c r="C132" s="13"/>
@@ -3771,7 +3771,7 @@
       <c r="Q132" s="8"/>
       <c r="R132" s="8"/>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" s="9"/>
       <c r="B133" s="9"/>
       <c r="C133" s="13"/>
@@ -3793,7 +3793,7 @@
       <c r="Q133" s="8"/>
       <c r="R133" s="8"/>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" s="9"/>
       <c r="B134" s="9"/>
       <c r="C134" s="13"/>
@@ -3815,7 +3815,7 @@
       <c r="Q134" s="8"/>
       <c r="R134" s="8"/>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" s="9"/>
       <c r="B135" s="9"/>
       <c r="C135" s="13"/>
@@ -3837,7 +3837,7 @@
       <c r="Q135" s="8"/>
       <c r="R135" s="8"/>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" s="9"/>
       <c r="B136" s="9"/>
       <c r="C136" s="13"/>
@@ -3859,7 +3859,7 @@
       <c r="Q136" s="8"/>
       <c r="R136" s="8"/>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" s="9"/>
       <c r="B137" s="9"/>
       <c r="C137" s="13"/>
@@ -3881,7 +3881,7 @@
       <c r="Q137" s="8"/>
       <c r="R137" s="8"/>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" s="9"/>
       <c r="B138" s="9"/>
       <c r="C138" s="13"/>
@@ -3903,7 +3903,7 @@
       <c r="Q138" s="8"/>
       <c r="R138" s="8"/>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" s="9"/>
       <c r="B139" s="9"/>
       <c r="C139" s="13"/>
@@ -3925,7 +3925,7 @@
       <c r="Q139" s="8"/>
       <c r="R139" s="8"/>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" s="9"/>
       <c r="B140" s="9"/>
       <c r="C140" s="13"/>
@@ -3947,7 +3947,7 @@
       <c r="Q140" s="8"/>
       <c r="R140" s="8"/>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" s="9"/>
       <c r="B141" s="9"/>
       <c r="C141" s="13"/>
@@ -3969,7 +3969,7 @@
       <c r="Q141" s="8"/>
       <c r="R141" s="8"/>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" s="9"/>
       <c r="B142" s="9"/>
       <c r="C142" s="13"/>
@@ -3991,7 +3991,7 @@
       <c r="Q142" s="8"/>
       <c r="R142" s="8"/>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" s="9"/>
       <c r="B143" s="9"/>
       <c r="C143" s="13"/>
@@ -4013,7 +4013,7 @@
       <c r="Q143" s="8"/>
       <c r="R143" s="8"/>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" s="9"/>
       <c r="B144" s="9"/>
       <c r="C144" s="13"/>
@@ -4035,7 +4035,7 @@
       <c r="Q144" s="8"/>
       <c r="R144" s="8"/>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" s="9"/>
       <c r="B145" s="9"/>
       <c r="C145" s="13"/>
@@ -4057,7 +4057,7 @@
       <c r="Q145" s="8"/>
       <c r="R145" s="8"/>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" s="9"/>
       <c r="B146" s="9"/>
       <c r="C146" s="13"/>
@@ -4079,7 +4079,7 @@
       <c r="Q146" s="8"/>
       <c r="R146" s="8"/>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" s="9"/>
       <c r="B147" s="9"/>
       <c r="C147" s="13"/>
@@ -4101,7 +4101,7 @@
       <c r="Q147" s="8"/>
       <c r="R147" s="8"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" s="9"/>
       <c r="B148" s="9"/>
       <c r="C148" s="13"/>
@@ -4123,7 +4123,7 @@
       <c r="Q148" s="8"/>
       <c r="R148" s="8"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" s="9"/>
       <c r="B149" s="9"/>
       <c r="C149" s="13"/>
@@ -4145,7 +4145,7 @@
       <c r="Q149" s="8"/>
       <c r="R149" s="8"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" s="9"/>
       <c r="B150" s="9"/>
       <c r="C150" s="13"/>
@@ -4167,7 +4167,7 @@
       <c r="Q150" s="8"/>
       <c r="R150" s="8"/>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" s="9"/>
       <c r="B151" s="9"/>
       <c r="C151" s="13"/>
@@ -4189,7 +4189,7 @@
       <c r="Q151" s="8"/>
       <c r="R151" s="8"/>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" s="9"/>
       <c r="B152" s="9"/>
       <c r="C152" s="13"/>
@@ -4211,7 +4211,7 @@
       <c r="Q152" s="8"/>
       <c r="R152" s="8"/>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" s="9"/>
       <c r="B153" s="9"/>
       <c r="C153" s="13"/>
@@ -4233,7 +4233,7 @@
       <c r="Q153" s="8"/>
       <c r="R153" s="8"/>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" s="9"/>
       <c r="B154" s="9"/>
       <c r="C154" s="13"/>
@@ -4255,7 +4255,7 @@
       <c r="Q154" s="8"/>
       <c r="R154" s="8"/>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" s="9"/>
       <c r="B155" s="9"/>
       <c r="C155" s="13"/>
@@ -4277,7 +4277,7 @@
       <c r="Q155" s="8"/>
       <c r="R155" s="8"/>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" s="9"/>
       <c r="B156" s="9"/>
       <c r="C156" s="13"/>
@@ -4299,7 +4299,7 @@
       <c r="Q156" s="8"/>
       <c r="R156" s="8"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" s="9"/>
       <c r="B157" s="9"/>
       <c r="C157" s="13"/>
@@ -4321,7 +4321,7 @@
       <c r="Q157" s="8"/>
       <c r="R157" s="8"/>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" s="9"/>
       <c r="B158" s="9"/>
       <c r="C158" s="13"/>
@@ -4343,7 +4343,7 @@
       <c r="Q158" s="8"/>
       <c r="R158" s="8"/>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" s="9"/>
       <c r="B159" s="9"/>
       <c r="C159" s="13"/>
@@ -4365,7 +4365,7 @@
       <c r="Q159" s="8"/>
       <c r="R159" s="8"/>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" s="9"/>
       <c r="B160" s="9"/>
       <c r="C160" s="13"/>
@@ -4387,7 +4387,7 @@
       <c r="Q160" s="8"/>
       <c r="R160" s="8"/>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" s="9"/>
       <c r="B161" s="9"/>
       <c r="C161" s="13"/>
@@ -4409,7 +4409,7 @@
       <c r="Q161" s="8"/>
       <c r="R161" s="8"/>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" s="9"/>
       <c r="B162" s="9"/>
       <c r="C162" s="13"/>
@@ -4431,7 +4431,7 @@
       <c r="Q162" s="8"/>
       <c r="R162" s="8"/>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" s="9"/>
       <c r="B163" s="9"/>
       <c r="C163" s="13"/>
@@ -4453,7 +4453,7 @@
       <c r="Q163" s="8"/>
       <c r="R163" s="8"/>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="9"/>
       <c r="B164" s="9"/>
       <c r="C164" s="13"/>
@@ -4475,7 +4475,7 @@
       <c r="Q164" s="8"/>
       <c r="R164" s="8"/>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" s="9"/>
       <c r="B165" s="9"/>
       <c r="C165" s="13"/>
@@ -4497,7 +4497,7 @@
       <c r="Q165" s="8"/>
       <c r="R165" s="8"/>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" s="9"/>
       <c r="B166" s="9"/>
       <c r="C166" s="13"/>
@@ -4519,7 +4519,7 @@
       <c r="Q166" s="8"/>
       <c r="R166" s="8"/>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" s="9"/>
       <c r="B167" s="9"/>
       <c r="C167" s="13"/>
@@ -4541,7 +4541,7 @@
       <c r="Q167" s="8"/>
       <c r="R167" s="8"/>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" s="9"/>
       <c r="B168" s="9"/>
       <c r="C168" s="13"/>
@@ -4563,7 +4563,7 @@
       <c r="Q168" s="8"/>
       <c r="R168" s="8"/>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" s="9"/>
       <c r="B169" s="9"/>
       <c r="C169" s="13"/>
@@ -4585,7 +4585,7 @@
       <c r="Q169" s="8"/>
       <c r="R169" s="8"/>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
       <c r="B170" s="6"/>
       <c r="C170" s="13"/>
@@ -4607,7 +4607,7 @@
       <c r="Q170" s="8"/>
       <c r="R170" s="8"/>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
       <c r="B171" s="6"/>
       <c r="C171" s="13"/>
@@ -4629,7 +4629,7 @@
       <c r="Q171" s="8"/>
       <c r="R171" s="8"/>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="13"/>
@@ -4651,7 +4651,7 @@
       <c r="Q172" s="8"/>
       <c r="R172" s="8"/>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
       <c r="B173" s="6"/>
       <c r="C173" s="13"/>
@@ -4673,7 +4673,7 @@
       <c r="Q173" s="8"/>
       <c r="R173" s="8"/>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
       <c r="B174" s="6"/>
       <c r="C174" s="13"/>
@@ -4695,7 +4695,7 @@
       <c r="Q174" s="8"/>
       <c r="R174" s="8"/>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" s="6"/>
       <c r="B175" s="6"/>
       <c r="C175" s="13"/>
@@ -4717,7 +4717,7 @@
       <c r="Q175" s="8"/>
       <c r="R175" s="8"/>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" s="6"/>
       <c r="B176" s="6"/>
       <c r="C176" s="13"/>
@@ -4739,7 +4739,7 @@
       <c r="Q176" s="8"/>
       <c r="R176" s="8"/>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
       <c r="B177" s="6"/>
       <c r="C177" s="13"/>
@@ -4761,7 +4761,7 @@
       <c r="Q177" s="8"/>
       <c r="R177" s="8"/>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
       <c r="B178" s="6"/>
       <c r="C178" s="13"/>
@@ -4783,7 +4783,7 @@
       <c r="Q178" s="8"/>
       <c r="R178" s="8"/>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" s="6"/>
       <c r="B179" s="6"/>
       <c r="C179" s="13"/>
@@ -4805,7 +4805,7 @@
       <c r="Q179" s="8"/>
       <c r="R179" s="8"/>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="6"/>
       <c r="B180" s="6"/>
       <c r="C180" s="13"/>
@@ -4827,7 +4827,7 @@
       <c r="Q180" s="8"/>
       <c r="R180" s="8"/>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="13"/>
@@ -4849,7 +4849,7 @@
       <c r="Q181" s="8"/>
       <c r="R181" s="8"/>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="6"/>
       <c r="B182" s="6"/>
       <c r="C182" s="13"/>
@@ -4871,7 +4871,7 @@
       <c r="Q182" s="8"/>
       <c r="R182" s="8"/>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="6"/>
       <c r="B183" s="6"/>
       <c r="C183" s="13"/>
@@ -4893,7 +4893,7 @@
       <c r="Q183" s="8"/>
       <c r="R183" s="8"/>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="6"/>
       <c r="B184" s="6"/>
       <c r="C184" s="13"/>
@@ -4915,7 +4915,7 @@
       <c r="Q184" s="8"/>
       <c r="R184" s="8"/>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="13"/>
@@ -4937,7 +4937,7 @@
       <c r="Q185" s="8"/>
       <c r="R185" s="8"/>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" s="6"/>
       <c r="B186" s="6"/>
       <c r="C186" s="13"/>
@@ -4959,7 +4959,7 @@
       <c r="Q186" s="8"/>
       <c r="R186" s="8"/>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
       <c r="B187" s="6"/>
       <c r="C187" s="13"/>
@@ -4981,7 +4981,7 @@
       <c r="Q187" s="8"/>
       <c r="R187" s="8"/>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" s="6"/>
       <c r="B188" s="6"/>
       <c r="C188" s="13"/>
@@ -5003,7 +5003,7 @@
       <c r="Q188" s="8"/>
       <c r="R188" s="8"/>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" s="6"/>
       <c r="B189" s="6"/>
       <c r="C189" s="13"/>
@@ -5025,7 +5025,7 @@
       <c r="Q189" s="8"/>
       <c r="R189" s="8"/>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" s="6"/>
       <c r="B190" s="6"/>
       <c r="C190" s="13"/>
@@ -5047,7 +5047,7 @@
       <c r="Q190" s="8"/>
       <c r="R190" s="8"/>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" s="6"/>
       <c r="B191" s="6"/>
       <c r="C191" s="13"/>
@@ -5069,7 +5069,7 @@
       <c r="Q191" s="8"/>
       <c r="R191" s="8"/>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" s="6"/>
       <c r="B192" s="6"/>
       <c r="C192" s="13"/>
@@ -5091,7 +5091,7 @@
       <c r="Q192" s="8"/>
       <c r="R192" s="8"/>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" s="6"/>
       <c r="B193" s="6"/>
       <c r="C193" s="13"/>
@@ -5113,7 +5113,7 @@
       <c r="Q193" s="8"/>
       <c r="R193" s="8"/>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" s="6"/>
       <c r="B194" s="6"/>
       <c r="C194" s="13"/>
@@ -5135,7 +5135,7 @@
       <c r="Q194" s="8"/>
       <c r="R194" s="8"/>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" s="6"/>
       <c r="B195" s="6"/>
       <c r="C195" s="13"/>
@@ -5157,7 +5157,7 @@
       <c r="Q195" s="8"/>
       <c r="R195" s="8"/>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" s="6"/>
       <c r="B196" s="6"/>
       <c r="C196" s="13"/>
@@ -5179,7 +5179,7 @@
       <c r="Q196" s="8"/>
       <c r="R196" s="8"/>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" s="6"/>
       <c r="B197" s="6"/>
       <c r="C197" s="13"/>
@@ -5201,7 +5201,7 @@
       <c r="Q197" s="8"/>
       <c r="R197" s="8"/>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" s="6"/>
       <c r="B198" s="6"/>
       <c r="C198" s="13"/>
@@ -5223,7 +5223,7 @@
       <c r="Q198" s="8"/>
       <c r="R198" s="8"/>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" s="6"/>
       <c r="B199" s="6"/>
       <c r="C199" s="13"/>
@@ -5245,7 +5245,7 @@
       <c r="Q199" s="8"/>
       <c r="R199" s="8"/>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" s="6"/>
       <c r="B200" s="6"/>
       <c r="C200" s="13"/>
@@ -5267,7 +5267,7 @@
       <c r="Q200" s="8"/>
       <c r="R200" s="8"/>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" s="6"/>
       <c r="B201" s="6"/>
       <c r="C201" s="13"/>
@@ -5289,7 +5289,7 @@
       <c r="Q201" s="8"/>
       <c r="R201" s="8"/>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
       <c r="B202" s="6"/>
       <c r="C202" s="13"/>
@@ -5311,7 +5311,7 @@
       <c r="Q202" s="8"/>
       <c r="R202" s="8"/>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" s="6"/>
       <c r="B203" s="6"/>
       <c r="C203" s="13"/>
@@ -5333,7 +5333,7 @@
       <c r="Q203" s="8"/>
       <c r="R203" s="8"/>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
       <c r="B204" s="6"/>
       <c r="C204" s="13"/>
@@ -5355,7 +5355,7 @@
       <c r="Q204" s="8"/>
       <c r="R204" s="8"/>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" s="6"/>
       <c r="B205" s="6"/>
       <c r="C205" s="13"/>
@@ -5377,7 +5377,7 @@
       <c r="Q205" s="8"/>
       <c r="R205" s="8"/>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
       <c r="B206" s="6"/>
       <c r="C206" s="13"/>
@@ -5399,7 +5399,7 @@
       <c r="Q206" s="8"/>
       <c r="R206" s="8"/>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
       <c r="B207" s="6"/>
       <c r="C207" s="13"/>
@@ -5421,7 +5421,7 @@
       <c r="Q207" s="8"/>
       <c r="R207" s="8"/>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
       <c r="B208" s="6"/>
       <c r="C208" s="13"/>
@@ -5443,7 +5443,7 @@
       <c r="Q208" s="8"/>
       <c r="R208" s="8"/>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" s="6"/>
       <c r="B209" s="6"/>
       <c r="C209" s="13"/>
@@ -5465,7 +5465,7 @@
       <c r="Q209" s="8"/>
       <c r="R209" s="8"/>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" s="6"/>
       <c r="B210" s="6"/>
       <c r="C210" s="13"/>
@@ -5487,7 +5487,7 @@
       <c r="Q210" s="8"/>
       <c r="R210" s="8"/>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" s="6"/>
       <c r="B211" s="6"/>
       <c r="C211" s="13"/>
@@ -5509,7 +5509,7 @@
       <c r="Q211" s="8"/>
       <c r="R211" s="8"/>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" s="6"/>
       <c r="B212" s="6"/>
       <c r="C212" s="13"/>
@@ -5531,7 +5531,7 @@
       <c r="Q212" s="8"/>
       <c r="R212" s="8"/>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" s="6"/>
       <c r="B213" s="6"/>
       <c r="C213" s="13"/>
@@ -5553,7 +5553,7 @@
       <c r="Q213" s="8"/>
       <c r="R213" s="8"/>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" s="6"/>
       <c r="B214" s="6"/>
       <c r="C214" s="13"/>
@@ -5575,7 +5575,7 @@
       <c r="Q214" s="8"/>
       <c r="R214" s="8"/>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" s="6"/>
       <c r="B215" s="6"/>
       <c r="C215" s="13"/>
@@ -5597,7 +5597,7 @@
       <c r="Q215" s="8"/>
       <c r="R215" s="8"/>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" s="6"/>
       <c r="B216" s="6"/>
       <c r="C216" s="13"/>
@@ -5619,7 +5619,7 @@
       <c r="Q216" s="8"/>
       <c r="R216" s="8"/>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" s="6"/>
       <c r="B217" s="6"/>
       <c r="C217" s="13"/>
@@ -5641,7 +5641,7 @@
       <c r="Q217" s="8"/>
       <c r="R217" s="8"/>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" s="6"/>
       <c r="B218" s="6"/>
       <c r="C218" s="13"/>
@@ -5663,7 +5663,7 @@
       <c r="Q218" s="8"/>
       <c r="R218" s="8"/>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" s="6"/>
       <c r="B219" s="6"/>
       <c r="C219" s="13"/>
@@ -5685,7 +5685,7 @@
       <c r="Q219" s="8"/>
       <c r="R219" s="8"/>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" s="6"/>
       <c r="B220" s="6"/>
       <c r="C220" s="13"/>
@@ -5707,7 +5707,7 @@
       <c r="Q220" s="8"/>
       <c r="R220" s="8"/>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" s="6"/>
       <c r="B221" s="6"/>
       <c r="C221" s="13"/>
@@ -5729,7 +5729,7 @@
       <c r="Q221" s="8"/>
       <c r="R221" s="8"/>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
       <c r="B222" s="6"/>
       <c r="C222" s="13"/>
@@ -5751,7 +5751,7 @@
       <c r="Q222" s="8"/>
       <c r="R222" s="8"/>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" s="6"/>
       <c r="B223" s="6"/>
       <c r="C223" s="13"/>
@@ -5773,7 +5773,7 @@
       <c r="Q223" s="8"/>
       <c r="R223" s="8"/>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" s="6"/>
       <c r="B224" s="6"/>
       <c r="C224" s="13"/>
@@ -5795,7 +5795,7 @@
       <c r="Q224" s="8"/>
       <c r="R224" s="8"/>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225" s="6"/>
       <c r="B225" s="6"/>
       <c r="C225" s="13"/>
@@ -5817,7 +5817,7 @@
       <c r="Q225" s="8"/>
       <c r="R225" s="8"/>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" s="6"/>
       <c r="B226" s="6"/>
       <c r="C226" s="13"/>
@@ -5839,7 +5839,7 @@
       <c r="Q226" s="8"/>
       <c r="R226" s="8"/>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" s="6"/>
       <c r="B227" s="6"/>
       <c r="C227" s="13"/>
@@ -5861,7 +5861,7 @@
       <c r="Q227" s="8"/>
       <c r="R227" s="8"/>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" s="6"/>
       <c r="B228" s="6"/>
       <c r="C228" s="13"/>
@@ -5883,7 +5883,7 @@
       <c r="Q228" s="8"/>
       <c r="R228" s="8"/>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" s="6"/>
       <c r="B229" s="6"/>
       <c r="C229" s="13"/>
@@ -5905,7 +5905,7 @@
       <c r="Q229" s="8"/>
       <c r="R229" s="8"/>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230" s="6"/>
       <c r="B230" s="6"/>
       <c r="C230" s="13"/>
@@ -5927,7 +5927,7 @@
       <c r="Q230" s="8"/>
       <c r="R230" s="8"/>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" s="6"/>
       <c r="B231" s="6"/>
       <c r="C231" s="13"/>
@@ -5949,7 +5949,7 @@
       <c r="Q231" s="8"/>
       <c r="R231" s="8"/>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" s="6"/>
       <c r="B232" s="6"/>
       <c r="C232" s="13"/>
@@ -5971,7 +5971,7 @@
       <c r="Q232" s="8"/>
       <c r="R232" s="8"/>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" s="6"/>
       <c r="B233" s="6"/>
       <c r="C233" s="13"/>
@@ -5993,7 +5993,7 @@
       <c r="Q233" s="8"/>
       <c r="R233" s="8"/>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" s="6"/>
       <c r="B234" s="6"/>
       <c r="C234" s="13"/>
@@ -6015,7 +6015,7 @@
       <c r="Q234" s="8"/>
       <c r="R234" s="8"/>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" s="6"/>
       <c r="B235" s="6"/>
       <c r="C235" s="13"/>
@@ -6037,7 +6037,7 @@
       <c r="Q235" s="8"/>
       <c r="R235" s="8"/>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236" s="6"/>
       <c r="B236" s="6"/>
       <c r="C236" s="13"/>
@@ -6059,7 +6059,7 @@
       <c r="Q236" s="8"/>
       <c r="R236" s="8"/>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237" s="6"/>
       <c r="B237" s="6"/>
       <c r="C237" s="13"/>
@@ -6081,7 +6081,7 @@
       <c r="Q237" s="8"/>
       <c r="R237" s="8"/>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238" s="6"/>
       <c r="B238" s="6"/>
       <c r="C238" s="13"/>
@@ -6103,7 +6103,7 @@
       <c r="Q238" s="8"/>
       <c r="R238" s="8"/>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239" s="6"/>
       <c r="B239" s="6"/>
       <c r="C239" s="13"/>
@@ -6125,7 +6125,7 @@
       <c r="Q239" s="8"/>
       <c r="R239" s="8"/>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240" s="6"/>
       <c r="B240" s="6"/>
       <c r="C240" s="13"/>
@@ -6147,7 +6147,7 @@
       <c r="Q240" s="8"/>
       <c r="R240" s="8"/>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241" s="6"/>
       <c r="B241" s="6"/>
       <c r="C241" s="13"/>
@@ -6169,7 +6169,7 @@
       <c r="Q241" s="8"/>
       <c r="R241" s="8"/>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
       <c r="B242" s="6"/>
       <c r="C242" s="13"/>
@@ -6191,7 +6191,7 @@
       <c r="Q242" s="8"/>
       <c r="R242" s="8"/>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243" s="6"/>
       <c r="B243" s="6"/>
       <c r="C243" s="13"/>
@@ -6213,7 +6213,7 @@
       <c r="Q243" s="8"/>
       <c r="R243" s="8"/>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244" s="6"/>
       <c r="B244" s="6"/>
       <c r="C244" s="13"/>
@@ -6235,7 +6235,7 @@
       <c r="Q244" s="8"/>
       <c r="R244" s="8"/>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A245" s="6"/>
       <c r="B245" s="6"/>
       <c r="C245" s="13"/>
@@ -6257,7 +6257,7 @@
       <c r="Q245" s="8"/>
       <c r="R245" s="8"/>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A246" s="6"/>
       <c r="B246" s="6"/>
       <c r="C246" s="13"/>
@@ -6279,7 +6279,7 @@
       <c r="Q246" s="8"/>
       <c r="R246" s="8"/>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A247" s="6"/>
       <c r="B247" s="6"/>
       <c r="C247" s="13"/>
@@ -6301,7 +6301,7 @@
       <c r="Q247" s="8"/>
       <c r="R247" s="8"/>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A248" s="6"/>
       <c r="B248" s="6"/>
       <c r="C248" s="13"/>
@@ -6323,7 +6323,7 @@
       <c r="Q248" s="8"/>
       <c r="R248" s="8"/>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A249" s="6"/>
       <c r="B249" s="6"/>
       <c r="C249" s="13"/>
@@ -6345,7 +6345,7 @@
       <c r="Q249" s="8"/>
       <c r="R249" s="8"/>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A250" s="6"/>
       <c r="B250" s="6"/>
       <c r="C250" s="13"/>
@@ -6367,7 +6367,7 @@
       <c r="Q250" s="8"/>
       <c r="R250" s="8"/>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A251" s="6"/>
       <c r="B251" s="6"/>
       <c r="C251" s="13"/>
@@ -6389,7 +6389,7 @@
       <c r="Q251" s="8"/>
       <c r="R251" s="8"/>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A252" s="6"/>
       <c r="B252" s="6"/>
       <c r="C252" s="13"/>
@@ -6411,7 +6411,7 @@
       <c r="Q252" s="8"/>
       <c r="R252" s="8"/>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253" s="6"/>
       <c r="B253" s="6"/>
       <c r="C253" s="13"/>
@@ -6433,7 +6433,7 @@
       <c r="Q253" s="8"/>
       <c r="R253" s="8"/>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A254" s="6"/>
       <c r="B254" s="6"/>
       <c r="C254" s="13"/>
@@ -6455,7 +6455,7 @@
       <c r="Q254" s="8"/>
       <c r="R254" s="8"/>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A255" s="6"/>
       <c r="B255" s="6"/>
       <c r="C255" s="13"/>
@@ -6477,7 +6477,7 @@
       <c r="Q255" s="8"/>
       <c r="R255" s="8"/>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A256" s="6"/>
       <c r="B256" s="6"/>
       <c r="C256" s="13"/>
@@ -6499,7 +6499,7 @@
       <c r="Q256" s="8"/>
       <c r="R256" s="8"/>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257" s="6"/>
       <c r="B257" s="6"/>
       <c r="C257" s="13"/>
@@ -6521,7 +6521,7 @@
       <c r="Q257" s="8"/>
       <c r="R257" s="8"/>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258" s="6"/>
       <c r="B258" s="6"/>
       <c r="C258" s="13"/>
@@ -6543,7 +6543,7 @@
       <c r="Q258" s="8"/>
       <c r="R258" s="8"/>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259" s="6"/>
       <c r="B259" s="6"/>
       <c r="C259" s="13"/>
@@ -6565,7 +6565,7 @@
       <c r="Q259" s="8"/>
       <c r="R259" s="8"/>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260" s="6"/>
       <c r="B260" s="6"/>
       <c r="C260" s="13"/>
@@ -6587,7 +6587,7 @@
       <c r="Q260" s="8"/>
       <c r="R260" s="8"/>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A261" s="6"/>
       <c r="B261" s="6"/>
       <c r="C261" s="13"/>
@@ -6609,7 +6609,7 @@
       <c r="Q261" s="8"/>
       <c r="R261" s="8"/>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A262" s="6"/>
       <c r="B262" s="6"/>
       <c r="C262" s="13"/>
@@ -6631,7 +6631,7 @@
       <c r="Q262" s="8"/>
       <c r="R262" s="8"/>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A263" s="6"/>
       <c r="B263" s="6"/>
       <c r="C263" s="13"/>
@@ -6653,7 +6653,7 @@
       <c r="Q263" s="8"/>
       <c r="R263" s="8"/>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A264" s="6"/>
       <c r="B264" s="6"/>
       <c r="C264" s="13"/>
@@ -6675,7 +6675,7 @@
       <c r="Q264" s="8"/>
       <c r="R264" s="8"/>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A265" s="6"/>
       <c r="B265" s="6"/>
       <c r="C265" s="13"/>
@@ -6697,7 +6697,7 @@
       <c r="Q265" s="8"/>
       <c r="R265" s="8"/>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A266" s="6"/>
       <c r="B266" s="6"/>
       <c r="C266" s="13"/>
@@ -6719,7 +6719,7 @@
       <c r="Q266" s="8"/>
       <c r="R266" s="8"/>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A267" s="6"/>
       <c r="B267" s="6"/>
       <c r="C267" s="13"/>
@@ -6741,7 +6741,7 @@
       <c r="Q267" s="8"/>
       <c r="R267" s="8"/>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A268" s="6"/>
       <c r="B268" s="6"/>
       <c r="C268" s="13"/>
@@ -6763,7 +6763,7 @@
       <c r="Q268" s="8"/>
       <c r="R268" s="8"/>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A269" s="6"/>
       <c r="B269" s="6"/>
       <c r="C269" s="13"/>
@@ -6785,7 +6785,7 @@
       <c r="Q269" s="8"/>
       <c r="R269" s="8"/>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A270" s="6"/>
       <c r="B270" s="6"/>
       <c r="C270" s="13"/>
@@ -6807,7 +6807,7 @@
       <c r="Q270" s="8"/>
       <c r="R270" s="8"/>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A271" s="6"/>
       <c r="B271" s="6"/>
       <c r="C271" s="13"/>
@@ -6829,7 +6829,7 @@
       <c r="Q271" s="8"/>
       <c r="R271" s="8"/>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A272" s="6"/>
       <c r="B272" s="6"/>
       <c r="C272" s="13"/>
@@ -6851,7 +6851,7 @@
       <c r="Q272" s="8"/>
       <c r="R272" s="8"/>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A273" s="6"/>
       <c r="B273" s="6"/>
       <c r="C273" s="13"/>
@@ -6873,7 +6873,7 @@
       <c r="Q273" s="8"/>
       <c r="R273" s="8"/>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A274" s="6"/>
       <c r="B274" s="6"/>
       <c r="C274" s="13"/>
@@ -6895,7 +6895,7 @@
       <c r="Q274" s="8"/>
       <c r="R274" s="8"/>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A275" s="6"/>
       <c r="B275" s="6"/>
       <c r="C275" s="13"/>
@@ -6917,7 +6917,7 @@
       <c r="Q275" s="8"/>
       <c r="R275" s="8"/>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A276" s="6"/>
       <c r="B276" s="6"/>
       <c r="C276" s="13"/>
@@ -6939,7 +6939,7 @@
       <c r="Q276" s="8"/>
       <c r="R276" s="8"/>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A277" s="6"/>
       <c r="B277" s="6"/>
       <c r="C277" s="13"/>
@@ -6961,7 +6961,7 @@
       <c r="Q277" s="8"/>
       <c r="R277" s="8"/>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A278" s="6"/>
       <c r="B278" s="6"/>
       <c r="C278" s="13"/>
@@ -6983,7 +6983,7 @@
       <c r="Q278" s="8"/>
       <c r="R278" s="8"/>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A279" s="6"/>
       <c r="B279" s="6"/>
       <c r="C279" s="13"/>
@@ -7005,7 +7005,7 @@
       <c r="Q279" s="8"/>
       <c r="R279" s="8"/>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A280" s="6"/>
       <c r="B280" s="6"/>
       <c r="C280" s="13"/>
@@ -7027,7 +7027,7 @@
       <c r="Q280" s="8"/>
       <c r="R280" s="8"/>
     </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A281" s="6"/>
       <c r="B281" s="6"/>
       <c r="C281" s="13"/>
@@ -7049,7 +7049,7 @@
       <c r="Q281" s="8"/>
       <c r="R281" s="8"/>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A282" s="6"/>
       <c r="B282" s="6"/>
       <c r="C282" s="13"/>
@@ -7071,7 +7071,7 @@
       <c r="Q282" s="8"/>
       <c r="R282" s="8"/>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A283" s="6"/>
       <c r="B283" s="6"/>
       <c r="C283" s="13"/>
@@ -7093,7 +7093,7 @@
       <c r="Q283" s="8"/>
       <c r="R283" s="8"/>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A284" s="6"/>
       <c r="B284" s="6"/>
       <c r="C284" s="13"/>
@@ -7115,7 +7115,7 @@
       <c r="Q284" s="8"/>
       <c r="R284" s="8"/>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A285" s="6"/>
       <c r="B285" s="6"/>
       <c r="C285" s="13"/>
@@ -7137,7 +7137,7 @@
       <c r="Q285" s="8"/>
       <c r="R285" s="8"/>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A286" s="6"/>
       <c r="B286" s="6"/>
       <c r="C286" s="13"/>
@@ -7159,7 +7159,7 @@
       <c r="Q286" s="8"/>
       <c r="R286" s="8"/>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A287" s="6"/>
       <c r="B287" s="6"/>
       <c r="C287" s="13"/>
@@ -7181,7 +7181,7 @@
       <c r="Q287" s="8"/>
       <c r="R287" s="8"/>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A288" s="6"/>
       <c r="B288" s="6"/>
       <c r="C288" s="13"/>
@@ -7203,7 +7203,7 @@
       <c r="Q288" s="8"/>
       <c r="R288" s="8"/>
     </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A289" s="6"/>
       <c r="B289" s="6"/>
       <c r="C289" s="13"/>
@@ -7225,7 +7225,7 @@
       <c r="Q289" s="8"/>
       <c r="R289" s="8"/>
     </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A290" s="6"/>
       <c r="B290" s="6"/>
       <c r="C290" s="13"/>
@@ -7247,7 +7247,7 @@
       <c r="Q290" s="8"/>
       <c r="R290" s="8"/>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A291" s="6"/>
       <c r="B291" s="6"/>
       <c r="C291" s="13"/>
@@ -7269,7 +7269,7 @@
       <c r="Q291" s="8"/>
       <c r="R291" s="8"/>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A292" s="6"/>
       <c r="B292" s="6"/>
       <c r="C292" s="13"/>
@@ -7291,7 +7291,7 @@
       <c r="Q292" s="8"/>
       <c r="R292" s="8"/>
     </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A293" s="6"/>
       <c r="B293" s="6"/>
       <c r="C293" s="13"/>
@@ -7313,7 +7313,7 @@
       <c r="Q293" s="8"/>
       <c r="R293" s="8"/>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A294" s="6"/>
       <c r="B294" s="6"/>
       <c r="C294" s="13"/>
@@ -7335,7 +7335,7 @@
       <c r="Q294" s="8"/>
       <c r="R294" s="8"/>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A295" s="6"/>
       <c r="B295" s="6"/>
       <c r="C295" s="13"/>
@@ -7357,7 +7357,7 @@
       <c r="Q295" s="8"/>
       <c r="R295" s="8"/>
     </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A296" s="6"/>
       <c r="B296" s="6"/>
       <c r="C296" s="13"/>
@@ -7379,7 +7379,7 @@
       <c r="Q296" s="8"/>
       <c r="R296" s="8"/>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A297" s="6"/>
       <c r="B297" s="6"/>
       <c r="C297" s="13"/>
@@ -7401,7 +7401,7 @@
       <c r="Q297" s="8"/>
       <c r="R297" s="8"/>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A298" s="6"/>
       <c r="B298" s="6"/>
       <c r="C298" s="13"/>
@@ -7473,23 +7473,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="84.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="84.90625" style="4" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="35.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1" ht="35.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -7505,13 +7505,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="83.75" customWidth="1"/>
+    <col min="2" max="2" width="83.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>4</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>9</v>
       </c>
@@ -7527,7 +7527,7 @@
         <v>43245</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="81" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" ht="84" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>10</v>
       </c>
@@ -7535,11 +7535,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
       <c r="B4" s="15"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>4</v>
       </c>
@@ -7547,7 +7547,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>9</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>42754</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" ht="70" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>10</v>
       </c>
@@ -7563,11 +7563,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="24"/>
       <c r="B8" s="15"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>4</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>9</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>42384</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="148.5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" ht="154" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
         <v>10</v>
       </c>
@@ -7591,10 +7591,10 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="15"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
         <v>4</v>
       </c>
@@ -7602,7 +7602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="81" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2" ht="84" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -7610,7 +7610,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
       <c r="B15" s="15"/>
     </row>
